--- a/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FOS</v>
+        <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Durward</v>
+        <v>Graciela</v>
       </c>
       <c r="C2" t="str">
-        <v>Kilback</v>
+        <v>Reichert</v>
       </c>
       <c r="D2" t="str">
         <v>13911</v>
@@ -502,13 +502,13 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>4021367515</v>
+        <v>7818384575</v>
       </c>
       <c r="N2" t="str">
-        <v>durward@yopmail.com</v>
+        <v>graciela@yopmail.com</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>yop</v>
       </c>
       <c r="P2" t="str">
         <v>bakori</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>resr</v>
+        <v>re35sr</v>
       </c>
     </row>
   </sheetData>
